--- a/Assets/Scripts/Core/Parser/Stage.xlsx
+++ b/Assets/Scripts/Core/Parser/Stage.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wnsrl\OneDrive\바탕 화면\Dev\IdleGameProject\Assets\Scripts\Core\Parser\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wnsrl\Desktop\Dev\IdleRPG\Assets\Scripts\Core\Parser\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A7B56E9-E9A5-4C6A-8884-EBB3783B97B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A104DCD0-D281-4FD2-B8F4-E6FAE76FC01B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5940" yWindow="2055" windowWidth="19710" windowHeight="12645" xr2:uid="{6A3B98CA-3AD0-4B4C-8BCF-D55454C11B3B}"/>
+    <workbookView xWindow="29970" yWindow="1170" windowWidth="21600" windowHeight="11295" xr2:uid="{6A3B98CA-3AD0-4B4C-8BCF-D55454C11B3B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="6">
   <si>
     <t>MonsterName</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -421,7 +421,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A9302AC-0182-4A8C-A154-E73C7706D75B}">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="16.125" customWidth="1"/>
@@ -483,6 +483,34 @@
         <v>10</v>
       </c>
     </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>1</v>
+      </c>
+      <c r="B5">
+        <v>2</v>
+      </c>
+      <c r="C5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D5">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>2</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6">
+        <v>30</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Assets/Scripts/Core/Parser/Stage.xlsx
+++ b/Assets/Scripts/Core/Parser/Stage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wnsrl\Desktop\Dev\IdleRPG\Assets\Scripts\Core\Parser\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A104DCD0-D281-4FD2-B8F4-E6FAE76FC01B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{496CDB07-C9BA-4AE1-86E9-0FA279AA9119}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="29970" yWindow="1170" windowWidth="21600" windowHeight="11295" xr2:uid="{6A3B98CA-3AD0-4B4C-8BCF-D55454C11B3B}"/>
   </bookViews>
@@ -56,7 +56,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>MON_GOBLIN</t>
+    <t>MON_ORC</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>

--- a/Assets/Scripts/Core/Parser/Stage.xlsx
+++ b/Assets/Scripts/Core/Parser/Stage.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wnsrl\Desktop\Dev\IdleRPG\Assets\Scripts\Core\Parser\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wnsrl\Documents\Idle_RPG_2\Assets\Scripts\Core\Parser\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{496CDB07-C9BA-4AE1-86E9-0FA279AA9119}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8192262B-A78A-4A2F-A7B8-441209246D57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29970" yWindow="1170" windowWidth="21600" windowHeight="11295" xr2:uid="{6A3B98CA-3AD0-4B4C-8BCF-D55454C11B3B}"/>
+    <workbookView xWindow="5475" yWindow="1095" windowWidth="21600" windowHeight="13785" xr2:uid="{6A3B98CA-3AD0-4B4C-8BCF-D55454C11B3B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="8">
   <si>
     <t>MonsterName</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -52,11 +52,19 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>MON_SKELETON</t>
+    <t>MON_ORC</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>MON_ORC</t>
+    <t>MON_BANDIT_ARCHER</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MON_BANDIT_LEADER</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MON_BANDIT_SHIELD</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -421,10 +429,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A9302AC-0182-4A8C-A154-E73C7706D75B}">
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="16.125" customWidth="1"/>
+    <col min="3" max="3" width="20.75" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
@@ -449,10 +457,10 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D2">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
@@ -460,13 +468,13 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3" t="s">
         <v>5</v>
       </c>
       <c r="D3">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
@@ -477,10 +485,10 @@
         <v>2</v>
       </c>
       <c r="C4" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D4">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
@@ -488,27 +496,223 @@
         <v>1</v>
       </c>
       <c r="B5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C5" t="s">
         <v>5</v>
       </c>
       <c r="D5">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6">
+        <v>1</v>
+      </c>
+      <c r="B6">
+        <v>3</v>
+      </c>
+      <c r="C6" t="s">
+        <v>6</v>
+      </c>
+      <c r="D6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>1</v>
+      </c>
+      <c r="B7">
+        <v>4</v>
+      </c>
+      <c r="C7" t="s">
+        <v>5</v>
+      </c>
+      <c r="D7">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>1</v>
+      </c>
+      <c r="B8">
+        <v>4</v>
+      </c>
+      <c r="C8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D8">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>1</v>
+      </c>
+      <c r="B9">
+        <v>5</v>
+      </c>
+      <c r="C9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D9">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>1</v>
+      </c>
+      <c r="B10">
+        <v>5</v>
+      </c>
+      <c r="C10" t="s">
+        <v>6</v>
+      </c>
+      <c r="D10">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>1</v>
+      </c>
+      <c r="B11">
+        <v>6</v>
+      </c>
+      <c r="C11" t="s">
+        <v>5</v>
+      </c>
+      <c r="D11">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>1</v>
+      </c>
+      <c r="B12">
+        <v>6</v>
+      </c>
+      <c r="C12" t="s">
+        <v>6</v>
+      </c>
+      <c r="D12">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>1</v>
+      </c>
+      <c r="B13">
+        <v>6</v>
+      </c>
+      <c r="C13" t="s">
+        <v>7</v>
+      </c>
+      <c r="D13">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <v>1</v>
+      </c>
+      <c r="B14">
+        <v>7</v>
+      </c>
+      <c r="C14" t="s">
+        <v>5</v>
+      </c>
+      <c r="D14">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <v>1</v>
+      </c>
+      <c r="B15">
+        <v>7</v>
+      </c>
+      <c r="C15" t="s">
+        <v>6</v>
+      </c>
+      <c r="D15">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <v>1</v>
+      </c>
+      <c r="B16">
+        <v>7</v>
+      </c>
+      <c r="C16" t="s">
+        <v>7</v>
+      </c>
+      <c r="D16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <v>1</v>
+      </c>
+      <c r="B17">
+        <v>8</v>
+      </c>
+      <c r="C17" t="s">
+        <v>6</v>
+      </c>
+      <c r="D17">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A18">
+        <v>1</v>
+      </c>
+      <c r="B18">
+        <v>9</v>
+      </c>
+      <c r="C18" t="s">
+        <v>6</v>
+      </c>
+      <c r="D18">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A19">
+        <v>1</v>
+      </c>
+      <c r="B19">
+        <v>10</v>
+      </c>
+      <c r="C19" t="s">
+        <v>4</v>
+      </c>
+      <c r="D19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A20">
         <v>2</v>
       </c>
-      <c r="B6">
-        <v>1</v>
-      </c>
-      <c r="C6" t="s">
-        <v>5</v>
-      </c>
-      <c r="D6">
-        <v>30</v>
+      <c r="B20">
+        <v>1</v>
+      </c>
+      <c r="C20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D20">
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Scripts/Core/Parser/Stage.xlsx
+++ b/Assets/Scripts/Core/Parser/Stage.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wnsrl\Documents\Idle_RPG_2\Assets\Scripts\Core\Parser\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8192262B-A78A-4A2F-A7B8-441209246D57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73B18903-2810-48F0-BA96-5647EA05362D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5475" yWindow="1095" windowWidth="21600" windowHeight="13785" xr2:uid="{6A3B98CA-3AD0-4B4C-8BCF-D55454C11B3B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6A3B98CA-3AD0-4B4C-8BCF-D55454C11B3B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -460,7 +460,7 @@
         <v>6</v>
       </c>
       <c r="D2">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">

--- a/Assets/Scripts/Core/Parser/Stage.xlsx
+++ b/Assets/Scripts/Core/Parser/Stage.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wnsrl\Documents\Idle_RPG_2\Assets\Scripts\Core\Parser\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\project-k\Assets\Scripts\Core\Parser\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73B18903-2810-48F0-BA96-5647EA05362D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{248F1C13-06BA-490E-A325-A60919F9D507}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6A3B98CA-3AD0-4B4C-8BCF-D55454C11B3B}"/>
   </bookViews>
@@ -133,9 +133,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 테마">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -173,7 +173,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -279,7 +279,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -421,7 +421,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -695,10 +695,10 @@
         <v>10</v>
       </c>
       <c r="C19" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D19">
-        <v>1</v>
+        <v>35</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">

--- a/Assets/Scripts/Core/Parser/Stage.xlsx
+++ b/Assets/Scripts/Core/Parser/Stage.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26327"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\project-k\Assets\Scripts\Core\Parser\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\GitHub\project-k\Assets\Scripts\Core\Parser\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{248F1C13-06BA-490E-A325-A60919F9D507}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12E78818-F53A-47CE-A71F-A49A5A03D606}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6A3B98CA-3AD0-4B4C-8BCF-D55454C11B3B}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="11">
   <si>
     <t>MonsterName</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -52,10 +52,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>MON_ORC</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>MON_BANDIT_ARCHER</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -65,6 +61,22 @@
   </si>
   <si>
     <t>MON_BANDIT_SHIELD</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ORC</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AMORED_ORC</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ORC_KING</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BANDIT_KING</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -133,9 +145,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 테마">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -173,7 +185,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -279,7 +291,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -421,7 +433,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -429,7 +441,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A9302AC-0182-4A8C-A154-E73C7706D75B}">
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D31"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="20.75" customWidth="1"/>
@@ -457,7 +469,7 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -471,7 +483,7 @@
         <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D3">
         <v>7</v>
@@ -485,7 +497,7 @@
         <v>2</v>
       </c>
       <c r="C4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D4">
         <v>3</v>
@@ -499,7 +511,7 @@
         <v>3</v>
       </c>
       <c r="C5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D5">
         <v>10</v>
@@ -513,7 +525,7 @@
         <v>3</v>
       </c>
       <c r="C6" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D6">
         <v>4</v>
@@ -527,7 +539,7 @@
         <v>4</v>
       </c>
       <c r="C7" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D7">
         <v>12</v>
@@ -541,7 +553,7 @@
         <v>4</v>
       </c>
       <c r="C8" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D8">
         <v>7</v>
@@ -555,7 +567,7 @@
         <v>5</v>
       </c>
       <c r="C9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D9">
         <v>12</v>
@@ -569,7 +581,7 @@
         <v>5</v>
       </c>
       <c r="C10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D10">
         <v>12</v>
@@ -583,7 +595,7 @@
         <v>6</v>
       </c>
       <c r="C11" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D11">
         <v>10</v>
@@ -597,7 +609,7 @@
         <v>6</v>
       </c>
       <c r="C12" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D12">
         <v>10</v>
@@ -611,7 +623,7 @@
         <v>6</v>
       </c>
       <c r="C13" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D13">
         <v>3</v>
@@ -625,7 +637,7 @@
         <v>7</v>
       </c>
       <c r="C14" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D14">
         <v>5</v>
@@ -639,7 +651,7 @@
         <v>7</v>
       </c>
       <c r="C15" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D15">
         <v>15</v>
@@ -653,7 +665,7 @@
         <v>7</v>
       </c>
       <c r="C16" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D16">
         <v>5</v>
@@ -667,7 +679,7 @@
         <v>8</v>
       </c>
       <c r="C17" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D17">
         <v>20</v>
@@ -681,7 +693,7 @@
         <v>9</v>
       </c>
       <c r="C18" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D18">
         <v>25</v>
@@ -695,7 +707,7 @@
         <v>10</v>
       </c>
       <c r="C19" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D19">
         <v>35</v>
@@ -703,16 +715,170 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B20">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="C20" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A21">
+        <v>2</v>
+      </c>
+      <c r="B21">
+        <v>1</v>
+      </c>
+      <c r="C21" t="s">
+        <v>7</v>
+      </c>
+      <c r="D21">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A22">
+        <v>2</v>
+      </c>
+      <c r="B22">
+        <v>2</v>
+      </c>
+      <c r="C22" t="s">
+        <v>8</v>
+      </c>
+      <c r="D22">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A23">
+        <v>2</v>
+      </c>
+      <c r="B23">
+        <v>3</v>
+      </c>
+      <c r="C23" t="s">
+        <v>7</v>
+      </c>
+      <c r="D23">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A24">
+        <v>2</v>
+      </c>
+      <c r="B24">
+        <v>4</v>
+      </c>
+      <c r="C24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D24">
         <v>12</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A25">
+        <v>2</v>
+      </c>
+      <c r="B25">
+        <v>5</v>
+      </c>
+      <c r="C25" t="s">
+        <v>7</v>
+      </c>
+      <c r="D25">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A26">
+        <v>2</v>
+      </c>
+      <c r="B26">
+        <v>6</v>
+      </c>
+      <c r="C26" t="s">
+        <v>8</v>
+      </c>
+      <c r="D26">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A27">
+        <v>2</v>
+      </c>
+      <c r="B27">
+        <v>7</v>
+      </c>
+      <c r="C27" t="s">
+        <v>7</v>
+      </c>
+      <c r="D27">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A28">
+        <v>2</v>
+      </c>
+      <c r="B28">
+        <v>8</v>
+      </c>
+      <c r="C28" t="s">
+        <v>8</v>
+      </c>
+      <c r="D28">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A29">
+        <v>2</v>
+      </c>
+      <c r="B29">
+        <v>9</v>
+      </c>
+      <c r="C29" t="s">
+        <v>7</v>
+      </c>
+      <c r="D29">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A30">
+        <v>2</v>
+      </c>
+      <c r="B30">
+        <v>10</v>
+      </c>
+      <c r="C30" t="s">
+        <v>8</v>
+      </c>
+      <c r="D30">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A31">
+        <v>2</v>
+      </c>
+      <c r="B31">
+        <v>11</v>
+      </c>
+      <c r="C31" t="s">
+        <v>9</v>
+      </c>
+      <c r="D31">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Scripts/Core/Parser/Stage.xlsx
+++ b/Assets/Scripts/Core/Parser/Stage.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26327"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\GitHub\project-k\Assets\Scripts\Core\Parser\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\project-k\Assets\Scripts\Core\Parser\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12E78818-F53A-47CE-A71F-A49A5A03D606}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{248F1C13-06BA-490E-A325-A60919F9D507}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6A3B98CA-3AD0-4B4C-8BCF-D55454C11B3B}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="8">
   <si>
     <t>MonsterName</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -52,6 +52,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>MON_ORC</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>MON_BANDIT_ARCHER</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -61,22 +65,6 @@
   </si>
   <si>
     <t>MON_BANDIT_SHIELD</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ORC</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>AMORED_ORC</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ORC_KING</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BANDIT_KING</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -145,9 +133,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 테마">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -185,7 +173,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -291,7 +279,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -433,7 +421,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -441,7 +429,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A9302AC-0182-4A8C-A154-E73C7706D75B}">
-  <dimension ref="A1:D31"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="20.75" customWidth="1"/>
@@ -469,7 +457,7 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -483,7 +471,7 @@
         <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D3">
         <v>7</v>
@@ -497,7 +485,7 @@
         <v>2</v>
       </c>
       <c r="C4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D4">
         <v>3</v>
@@ -511,7 +499,7 @@
         <v>3</v>
       </c>
       <c r="C5" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D5">
         <v>10</v>
@@ -525,7 +513,7 @@
         <v>3</v>
       </c>
       <c r="C6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D6">
         <v>4</v>
@@ -539,7 +527,7 @@
         <v>4</v>
       </c>
       <c r="C7" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D7">
         <v>12</v>
@@ -553,7 +541,7 @@
         <v>4</v>
       </c>
       <c r="C8" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D8">
         <v>7</v>
@@ -567,7 +555,7 @@
         <v>5</v>
       </c>
       <c r="C9" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D9">
         <v>12</v>
@@ -581,7 +569,7 @@
         <v>5</v>
       </c>
       <c r="C10" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D10">
         <v>12</v>
@@ -595,7 +583,7 @@
         <v>6</v>
       </c>
       <c r="C11" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D11">
         <v>10</v>
@@ -609,7 +597,7 @@
         <v>6</v>
       </c>
       <c r="C12" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D12">
         <v>10</v>
@@ -623,7 +611,7 @@
         <v>6</v>
       </c>
       <c r="C13" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D13">
         <v>3</v>
@@ -637,7 +625,7 @@
         <v>7</v>
       </c>
       <c r="C14" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D14">
         <v>5</v>
@@ -651,7 +639,7 @@
         <v>7</v>
       </c>
       <c r="C15" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D15">
         <v>15</v>
@@ -665,7 +653,7 @@
         <v>7</v>
       </c>
       <c r="C16" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D16">
         <v>5</v>
@@ -679,7 +667,7 @@
         <v>8</v>
       </c>
       <c r="C17" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D17">
         <v>20</v>
@@ -693,7 +681,7 @@
         <v>9</v>
       </c>
       <c r="C18" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D18">
         <v>25</v>
@@ -707,7 +695,7 @@
         <v>10</v>
       </c>
       <c r="C19" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D19">
         <v>35</v>
@@ -715,170 +703,16 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B20">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C20" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D20">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A21">
-        <v>2</v>
-      </c>
-      <c r="B21">
-        <v>1</v>
-      </c>
-      <c r="C21" t="s">
-        <v>7</v>
-      </c>
-      <c r="D21">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A22">
-        <v>2</v>
-      </c>
-      <c r="B22">
-        <v>2</v>
-      </c>
-      <c r="C22" t="s">
-        <v>8</v>
-      </c>
-      <c r="D22">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A23">
-        <v>2</v>
-      </c>
-      <c r="B23">
-        <v>3</v>
-      </c>
-      <c r="C23" t="s">
-        <v>7</v>
-      </c>
-      <c r="D23">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A24">
-        <v>2</v>
-      </c>
-      <c r="B24">
-        <v>4</v>
-      </c>
-      <c r="C24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D24">
         <v>12</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A25">
-        <v>2</v>
-      </c>
-      <c r="B25">
-        <v>5</v>
-      </c>
-      <c r="C25" t="s">
-        <v>7</v>
-      </c>
-      <c r="D25">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A26">
-        <v>2</v>
-      </c>
-      <c r="B26">
-        <v>6</v>
-      </c>
-      <c r="C26" t="s">
-        <v>8</v>
-      </c>
-      <c r="D26">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A27">
-        <v>2</v>
-      </c>
-      <c r="B27">
-        <v>7</v>
-      </c>
-      <c r="C27" t="s">
-        <v>7</v>
-      </c>
-      <c r="D27">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A28">
-        <v>2</v>
-      </c>
-      <c r="B28">
-        <v>8</v>
-      </c>
-      <c r="C28" t="s">
-        <v>8</v>
-      </c>
-      <c r="D28">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A29">
-        <v>2</v>
-      </c>
-      <c r="B29">
-        <v>9</v>
-      </c>
-      <c r="C29" t="s">
-        <v>7</v>
-      </c>
-      <c r="D29">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A30">
-        <v>2</v>
-      </c>
-      <c r="B30">
-        <v>10</v>
-      </c>
-      <c r="C30" t="s">
-        <v>8</v>
-      </c>
-      <c r="D30">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A31">
-        <v>2</v>
-      </c>
-      <c r="B31">
-        <v>11</v>
-      </c>
-      <c r="C31" t="s">
-        <v>9</v>
-      </c>
-      <c r="D31">
-        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Scripts/Core/Parser/Stage.xlsx
+++ b/Assets/Scripts/Core/Parser/Stage.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26327"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\GitHub\project-k\Assets\Scripts\Core\Parser\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\project-k\Assets\Scripts\Core\Parser\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12E78818-F53A-47CE-A71F-A49A5A03D606}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{563A4352-C0DC-4E2E-A058-A1604B9F9044}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6A3B98CA-3AD0-4B4C-8BCF-D55454C11B3B}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6A3B98CA-3AD0-4B4C-8BCF-D55454C11B3B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,6 +28,9 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -145,9 +148,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 테마">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -185,7 +188,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -291,7 +294,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -433,7 +436,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -442,12 +445,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A9302AC-0182-4A8C-A154-E73C7706D75B}">
   <dimension ref="A1:D31"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="3" max="3" width="20.75" customWidth="1"/>
+    <col min="3" max="3" width="20.69921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -461,7 +464,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A2">
         <v>1</v>
       </c>
@@ -475,7 +478,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A3">
         <v>1</v>
       </c>
@@ -489,7 +492,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A4">
         <v>1</v>
       </c>
@@ -503,7 +506,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A5">
         <v>1</v>
       </c>
@@ -517,7 +520,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A6">
         <v>1</v>
       </c>
@@ -531,7 +534,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A7">
         <v>1</v>
       </c>
@@ -545,7 +548,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A8">
         <v>1</v>
       </c>
@@ -559,7 +562,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A9">
         <v>1</v>
       </c>
@@ -573,7 +576,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A10">
         <v>1</v>
       </c>
@@ -587,7 +590,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A11">
         <v>1</v>
       </c>
@@ -601,7 +604,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A12">
         <v>1</v>
       </c>
@@ -615,7 +618,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A13">
         <v>1</v>
       </c>
@@ -629,7 +632,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A14">
         <v>1</v>
       </c>
@@ -643,7 +646,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A15">
         <v>1</v>
       </c>
@@ -657,7 +660,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A16">
         <v>1</v>
       </c>
@@ -671,7 +674,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A17">
         <v>1</v>
       </c>
@@ -685,7 +688,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A18">
         <v>1</v>
       </c>
@@ -699,7 +702,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A19">
         <v>1</v>
       </c>
@@ -713,7 +716,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A20">
         <v>1</v>
       </c>
@@ -727,7 +730,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A21">
         <v>2</v>
       </c>
@@ -741,7 +744,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A22">
         <v>2</v>
       </c>
@@ -755,7 +758,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A23">
         <v>2</v>
       </c>
@@ -769,7 +772,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A24">
         <v>2</v>
       </c>
@@ -783,7 +786,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A25">
         <v>2</v>
       </c>
@@ -797,7 +800,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A26">
         <v>2</v>
       </c>
@@ -811,7 +814,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A27">
         <v>2</v>
       </c>
@@ -825,7 +828,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A28">
         <v>2</v>
       </c>
@@ -839,7 +842,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A29">
         <v>2</v>
       </c>
@@ -853,7 +856,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A30">
         <v>2</v>
       </c>
@@ -867,7 +870,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A31">
         <v>2</v>
       </c>
